--- a/data/trans_dic/P37A$medicoenfermedad-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicoenfermedad-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,62</t>
+          <t>3,11; 6,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,17</t>
+          <t>2,28; 5,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,94</t>
+          <t>2,14; 5,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,92</t>
+          <t>3,31; 6,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,29</t>
+          <t>1,8; 4,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,17</t>
+          <t>2,43; 5,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,16</t>
+          <t>3,07; 6,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,42</t>
+          <t>5,22; 7,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,75</t>
+          <t>2,8; 4,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,68</t>
+          <t>2,63; 4,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,01</t>
+          <t>2,93; 5,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,17</t>
+          <t>4,6; 6,5</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,11</t>
+          <t>1,98; 4,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,62</t>
+          <t>2,43; 4,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,89</t>
+          <t>2,48; 4,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,22</t>
+          <t>4,34; 7,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,18</t>
+          <t>1,9; 4,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,42</t>
+          <t>2,99; 5,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,75</t>
+          <t>1,72; 3,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,58</t>
+          <t>5,26; 7,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,85</t>
+          <t>2,2; 3,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,75</t>
+          <t>3,04; 4,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,0</t>
+          <t>2,39; 3,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,34</t>
+          <t>5,15; 6,98</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,44</t>
+          <t>2,49; 5,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,38</t>
+          <t>2,21; 5,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,35</t>
+          <t>3,14; 6,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,46</t>
+          <t>3,29; 6,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,86</t>
+          <t>1,64; 4,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,38</t>
+          <t>2,27; 5,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,48</t>
+          <t>1,32; 3,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,19</t>
+          <t>3,59; 6,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,18</t>
+          <t>2,37; 4,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,93</t>
+          <t>2,66; 4,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,46</t>
+          <t>2,47; 4,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,09</t>
+          <t>3,75; 5,52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,22</t>
+          <t>2,05; 4,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,53</t>
+          <t>2,96; 5,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,79</t>
+          <t>1,69; 3,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,19</t>
+          <t>5,76; 9,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,93</t>
+          <t>1,83; 3,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,83</t>
+          <t>3,25; 5,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,54</t>
+          <t>2,14; 4,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,12</t>
+          <t>6,26; 8,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,7</t>
+          <t>2,15; 3,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,29</t>
+          <t>3,39; 5,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,86</t>
+          <t>2,23; 3,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 8,14</t>
+          <t>6,36; 8,27</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,1</t>
+          <t>2,86; 4,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 4,37</t>
+          <t>3,04; 4,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,15</t>
+          <t>2,86; 4,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 6,16</t>
+          <t>4,93; 6,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,4</t>
+          <t>2,24; 3,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 4,68</t>
+          <t>3,27; 4,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,64</t>
+          <t>2,45; 3,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,63; 6,43</t>
+          <t>5,72; 6,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,55</t>
+          <t>2,7; 3,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,38; 4,36</t>
+          <t>3,36; 4,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,67</t>
+          <t>2,87; 3,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,09</t>
+          <t>5,54; 6,49</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>31566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43605</t>
+          <t>47225</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70725</t>
+          <t>78792</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21919; 45954</t>
+          <t>21602; 43292</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16025; 36337</t>
+          <t>16038; 36634</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14065; 33305</t>
+          <t>14422; 35125</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19261; 37591</t>
+          <t>22869; 43230</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12337; 29538</t>
+          <t>12378; 29300</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15916; 36020</t>
+          <t>16966; 35752</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19502; 41441</t>
+          <t>20650; 42351</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32837; 53820</t>
+          <t>38349; 57980</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38414; 65676</t>
+          <t>38754; 67738</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36911; 65614</t>
+          <t>36849; 65043</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39974; 67457</t>
+          <t>39470; 68353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56997; 83939</t>
+          <t>65603; 92666</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53426</t>
+          <t>58276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>59349</t>
+          <t>68972</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>112774</t>
+          <t>127248</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18905; 39572</t>
+          <t>19013; 41823</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24294; 46993</t>
+          <t>24768; 48324</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24918; 49979</t>
+          <t>25327; 49550</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23884; 74147</t>
+          <t>45472; 73668</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19257; 40493</t>
+          <t>18393; 39956</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29976; 55990</t>
+          <t>30886; 56057</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16572; 39135</t>
+          <t>17902; 41155</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47963; 72629</t>
+          <t>56381; 85093</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42648; 74356</t>
+          <t>42466; 72979</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60394; 97312</t>
+          <t>62356; 97009</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46807; 82676</t>
+          <t>49359; 81802</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73455; 136351</t>
+          <t>109122; 148024</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32471</t>
+          <t>36091</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33252</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65723</t>
+          <t>74280</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17134; 36903</t>
+          <t>16871; 36929</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17570; 40736</t>
+          <t>16718; 40171</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24473; 48211</t>
+          <t>23868; 47587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24269; 45507</t>
+          <t>26394; 51336</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11187; 26412</t>
+          <t>11202; 27496</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18614; 41820</t>
+          <t>17668; 40587</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11422; 27322</t>
+          <t>10334; 27487</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14831; 48428</t>
+          <t>29185; 49051</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31097; 56891</t>
+          <t>32307; 57738</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41788; 75696</t>
+          <t>40884; 72948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40518; 68825</t>
+          <t>38129; 67486</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44033; 83389</t>
+          <t>60515; 89189</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67978</t>
+          <t>71169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>74574</t>
+          <t>81904</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>142552</t>
+          <t>153073</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19379; 39808</t>
+          <t>19289; 38973</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26865; 52399</t>
+          <t>28020; 54284</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16274; 35530</t>
+          <t>15810; 35074</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53244; 85192</t>
+          <t>57028; 89989</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18683; 40849</t>
+          <t>18957; 39846</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34365; 61282</t>
+          <t>34218; 61461</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21348; 47423</t>
+          <t>22327; 45995</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>56850; 88861</t>
+          <t>70096; 97373</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43332; 73266</t>
+          <t>42657; 71380</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>68664; 105774</t>
+          <t>67859; 106284</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44182; 76435</t>
+          <t>44215; 74873</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>120434; 164603</t>
+          <t>134195; 174346</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180994</t>
+          <t>197102</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>210781</t>
+          <t>236290</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>391775</t>
+          <t>433392</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>92818; 134187</t>
+          <t>93850; 134078</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>104290; 149818</t>
+          <t>104014; 153414</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97872; 140840</t>
+          <t>97222; 140278</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>144690; 213009</t>
+          <t>174010; 226084</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>76264; 114793</t>
+          <t>75676; 112191</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>119979; 166399</t>
+          <t>116341; 164928</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86925; 129041</t>
+          <t>86840; 130473</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>172014; 238691</t>
+          <t>213731; 260319</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>180170; 236111</t>
+          <t>179404; 232890</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>236250; 304336</t>
+          <t>234629; 305274</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>197047; 254881</t>
+          <t>198917; 256454</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>340406; 436642</t>
+          <t>402625; 471890</t>
         </is>
       </c>
     </row>
